--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -36,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +84,13 @@
       <color rgb="007A8194"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B6B2F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +110,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F1F3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -188,6 +198,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -20589,9 +20602,9 @@
         </is>
       </c>
       <c r="T3" s="16" t="inlineStr"/>
-      <c r="U3" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="U3" s="21" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="V3" s="16" t="inlineStr">
@@ -20599,12 +20612,20 @@
           <t>Othman</t>
         </is>
       </c>
-      <c r="W3" s="16" t="inlineStr"/>
-      <c r="X3" s="16" t="inlineStr"/>
+      <c r="W3" s="16" t="inlineStr">
+        <is>
+          <t>42601e8</t>
+        </is>
+      </c>
+      <c r="X3" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="Y3" s="16" t="inlineStr"/>
       <c r="Z3" s="16" t="inlineStr">
         <is>
-          <t>Reported as 'page design is terrible and size page not fit the browser page'. Split from the design rework, which is tracked as CR-011.</t>
+          <t>Majeur → confirmé MOBILE UNIQUEMENT. Aucun débordement sur ordinateur (1280/1366/1440/1920 = 0). Cause : halo décoratif de 440px sans overflow-hidden. Le grief « ne rentre pas » sur grand écran est un sujet de DESIGN, suivi en CR-011.</t>
         </is>
       </c>
     </row>
@@ -20707,9 +20728,9 @@
         </is>
       </c>
       <c r="T4" s="16" t="inlineStr"/>
-      <c r="U4" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="U4" s="21" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="V4" s="16" t="inlineStr">
@@ -20717,12 +20738,20 @@
           <t>Othman</t>
         </is>
       </c>
-      <c r="W4" s="16" t="inlineStr"/>
-      <c r="X4" s="16" t="inlineStr"/>
+      <c r="W4" s="16" t="inlineStr">
+        <is>
+          <t>42601e8</t>
+        </is>
+      </c>
+      <c r="X4" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="Y4" s="16" t="inlineStr"/>
       <c r="Z4" s="16" t="inlineStr">
         <is>
-          <t>List the exact elements in the Test Log before fixing. e2e/outil.audit-clics.mjs already detects dead buttons — run it first to get the full list.</t>
+          <t>Requalifié. Aucun élément TROMPEUR sur les 7 tableaux de bord. Réel : 3 chiffres de la console plateforme sans `to` ni `onClick` → rendus en &lt;div&gt; inerte. Les 4 mènent désormais à #/app/schools (vérifié en production).</t>
         </is>
       </c>
     </row>
@@ -20824,9 +20853,9 @@
         </is>
       </c>
       <c r="T5" s="16" t="inlineStr"/>
-      <c r="U5" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="U5" s="21" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="V5" s="16" t="inlineStr">
@@ -20834,12 +20863,20 @@
           <t>Othman</t>
         </is>
       </c>
-      <c r="W5" s="16" t="inlineStr"/>
-      <c r="X5" s="16" t="inlineStr"/>
+      <c r="W5" s="16" t="inlineStr">
+        <is>
+          <t>42601e8</t>
+        </is>
+      </c>
+      <c r="X5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="Y5" s="16" t="inlineStr"/>
       <c r="Z5" s="16" t="inlineStr">
         <is>
-          <t>This is the defect half of note 6. Turning the one-pager into real routed pages is a separate product decision, tracked as CR-006.</t>
+          <t>Requalifié MINEUR → MAJEUR. Les liens ne « défilaient » pas : ils ne faisaient RIEN. Incompatibilité &lt;a href=#ancre&gt; / HashRouter — 9 liens morts. Corrigé + état actif ajouté. Vérifié en production : 0 → 1979.</t>
         </is>
       </c>
     </row>
@@ -20941,9 +20978,9 @@
         </is>
       </c>
       <c r="T6" s="16" t="inlineStr"/>
-      <c r="U6" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="U6" s="21" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="V6" s="16" t="inlineStr">
@@ -20951,12 +20988,20 @@
           <t>Othman</t>
         </is>
       </c>
-      <c r="W6" s="16" t="inlineStr"/>
-      <c r="X6" s="16" t="inlineStr"/>
+      <c r="W6" s="16" t="inlineStr">
+        <is>
+          <t>42601e8</t>
+        </is>
+      </c>
+      <c r="X6" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
       <c r="Y6" s="16" t="inlineStr"/>
       <c r="Z6" s="16" t="inlineStr">
         <is>
-          <t>Check at several widths — likely a flex alignment issue, so it may only show at some breakpoints.</t>
+          <t>Confirmé. Cause : la ligne de base d'un conteneur flex vient de son premier élément ; ici une icône SVG, sans ligne de base. Icône passée en inline.</t>
         </is>
       </c>
     </row>
@@ -32272,7 +32317,7 @@
       </c>
       <c r="O3" s="16" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>TRIAGED</t>
         </is>
       </c>
       <c r="P3" s="16" t="inlineStr"/>
@@ -32283,7 +32328,11 @@
         </is>
       </c>
       <c r="S3" s="16" t="inlineStr"/>
-      <c r="T3" s="16" t="inlineStr"/>
+      <c r="T3" s="16" t="inlineStr">
+        <is>
+          <t>PAS un remplacer-tout. 1108 occurrences : 457 en commentaires (à laisser), 49 dans t() — où la chaîne FRANÇAISE est la CLÉ de traduction : la modifier casse l'arabe en silence, sans qu'aucun test n'échoue. Il faut modifier l'appel ET la clé i18n.js dans le même geste, et choisir au cas par cas (· ici, virgule là). ~600 décisions : mérite une passe dédiée.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="108" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -32772,12 +32821,16 @@
           <t>S</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P9" s="16" t="inlineStr"/>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t>42601e8 · 2026-07-22</t>
+        </is>
+      </c>
       <c r="Q9" s="16" t="inlineStr"/>
       <c r="R9" s="16" t="inlineStr">
         <is>
@@ -32785,7 +32838,11 @@
         </is>
       </c>
       <c r="S9" s="16" t="inlineStr"/>
-      <c r="T9" s="16" t="inlineStr"/>
+      <c r="T9" s="16" t="inlineStr">
+        <is>
+          <t>Formulaire élargi (max-w-2xl → max-w-4xl). Vérifié : toujours 0 débordement à 390px.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="108" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -33121,7 +33178,11 @@
           <t>DEF-001</t>
         </is>
       </c>
-      <c r="T13" s="16" t="inlineStr"/>
+      <c r="T13" s="16" t="inlineStr">
+        <is>
+          <t>Porte désormais AUSSI le grief « la page ne rentre pas » sur grand écran : la mesure montre 0 débordement sur ordinateur, donc c'est du design, pas un défaut. Le débordement mobile réel a été corrigé (DEF-001, clos).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="108" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
@@ -33274,12 +33335,16 @@
           <t>M</t>
         </is>
       </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr"/>
+      <c r="O15" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P15" s="16" t="inlineStr">
+        <is>
+          <t>42601e8 · 2026-07-22</t>
+        </is>
+      </c>
       <c r="Q15" s="16" t="inlineStr"/>
       <c r="R15" s="16" t="inlineStr">
         <is>
@@ -33287,7 +33352,11 @@
         </is>
       </c>
       <c r="S15" s="16" t="inlineStr"/>
-      <c r="T15" s="16" t="inlineStr"/>
+      <c r="T15" s="16" t="inlineStr">
+        <is>
+          <t>Livré. Serveur : /api/forgot + /api/reset, jeton usage unique 60 min, réponse neutre, 5 demandes/h/IP, compte désactivé ignoré, sessions fermées à la réinitialisation. Web : #/mot-de-passe-oublie + #/reinitialiser + lien sur /login. Mode démo : la demande part à support@kogiagroup.com. 4 tests serveur + 10 vérif. navigateur.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="108" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
@@ -33440,12 +33509,16 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="O17" s="16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="P17" s="16" t="inlineStr"/>
+      <c r="O17" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P17" s="16" t="inlineStr">
+        <is>
+          <t>42601e8 · 2026-07-22</t>
+        </is>
+      </c>
       <c r="Q17" s="16" t="inlineStr"/>
       <c r="R17" s="16" t="inlineStr">
         <is>
@@ -33453,7 +33526,11 @@
         </is>
       </c>
       <c r="S17" s="16" t="inlineStr"/>
-      <c r="T17" s="16" t="inlineStr"/>
+      <c r="T17" s="16" t="inlineStr">
+        <is>
+          <t>Chip météo en une seule ligne (icône 20px + température) ; libellé et détail dans le panneau.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="108" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
@@ -39390,27 +39467,77 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="16" t="n"/>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16" t="n"/>
-      <c r="H3" s="16" t="n"/>
-      <c r="I3" s="16" t="n"/>
-      <c r="J3" s="16" t="n"/>
-      <c r="K3" s="16" t="n"/>
+    <row r="3" ht="64" customHeight="1">
+      <c r="A3" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Recette QA initiale</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>42601e8</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Othman + Claude</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>Pages publiques (accueil, connexion, pré-inscription) × 6 tailles ; tableaux de bord × 7 rôles ; parcours mot de passe oublié ; suites automatisées complètes.</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="I3" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J3" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="L3" s="18">
         <f>IF(N(H3)=0,"",I3/H3)</f>
         <v/>
       </c>
-      <c r="M3" s="16" t="n"/>
-      <c r="N3" s="16" t="n"/>
-      <c r="O3" s="16" t="n"/>
-      <c r="P3" s="16" t="n"/>
-      <c r="Q3" s="16" t="n"/>
+      <c r="M3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="21" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="inlineStr">
+        <is>
+          <t>4 défauts trouvés et corrigés le jour même. 3 demandes livrées. core 54/54 · serveur 15/15 · e2e 131/131 · CI verte · vérifié sur le site réel.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n"/>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -36,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,8 +94,13 @@
       <color rgb="008A5A00"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +132,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -154,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -212,6 +222,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -33685,12 +33698,16 @@
           <t>M</t>
         </is>
       </c>
-      <c r="O18" s="22" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="P18" s="16" t="inlineStr"/>
+      <c r="O18" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P18" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q18" s="16" t="inlineStr"/>
       <c r="R18" s="16" t="inlineStr">
         <is>
@@ -33700,7 +33717,7 @@
       <c r="S18" s="16" t="inlineStr"/>
       <c r="T18" s="16" t="inlineStr">
         <is>
-          <t>Recherche du modèle de rôles (Direction vs Administration) en cours : document en préparation.</t>
+          <t>Tranché et documenté (docs/quality/role-model.md §2) : l’Administration PRÉPARE et enregistre ; la Direction DÉCIDE et approuve. Jamais le même compte sur l’argent ou une action RH. Recherche sourcée (9 références).</t>
         </is>
       </c>
     </row>
@@ -33785,7 +33802,11 @@
         </is>
       </c>
       <c r="S19" s="16" t="inlineStr"/>
-      <c r="T19" s="16" t="inlineStr"/>
+      <c r="T19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman. </t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="108" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -33868,7 +33889,11 @@
         </is>
       </c>
       <c r="S20" s="16" t="inlineStr"/>
-      <c r="T20" s="16" t="inlineStr"/>
+      <c r="T20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman. </t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="108" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -33951,7 +33976,11 @@
         </is>
       </c>
       <c r="S21" s="16" t="inlineStr"/>
-      <c r="T21" s="16" t="inlineStr"/>
+      <c r="T21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman. </t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="108" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -34021,12 +34050,16 @@
           <t>L</t>
         </is>
       </c>
-      <c r="O22" s="22" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="P22" s="16" t="inlineStr"/>
+      <c r="O22" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P22" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q22" s="16" t="inlineStr"/>
       <c r="R22" s="16" t="inlineStr">
         <is>
@@ -34036,7 +34069,7 @@
       <c r="S22" s="16" t="inlineStr"/>
       <c r="T22" s="16" t="inlineStr">
         <is>
-          <t>Recherche des relations entre tous les rôles × niveaux en cours.</t>
+          <t>Modèle complet livré (docs/quality/role-model.md) : les 8 rôles POSSÈDE/DÉCIDE/APPROUVE/NE-DOIT-PAS, les chaînes d’approbation, la matrice « ne doit pas voir », et les différences crèche vs primaire. Devient la spéc de CR-019/021.</t>
         </is>
       </c>
     </row>
@@ -34121,7 +34154,11 @@
         </is>
       </c>
       <c r="S23" s="16" t="inlineStr"/>
-      <c r="T23" s="16" t="inlineStr"/>
+      <c r="T23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman. </t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="108" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -34214,49 +34251,189 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16" t="n"/>
-      <c r="I25" s="16" t="n"/>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
-      <c r="M25" s="16" t="n"/>
-      <c r="N25" s="16" t="n"/>
-      <c r="O25" s="16" t="n"/>
-      <c r="P25" s="16" t="n"/>
-      <c r="Q25" s="16" t="n"/>
-      <c r="R25" s="16" t="n"/>
-      <c r="S25" s="16" t="n"/>
-      <c r="T25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="16" t="n"/>
-      <c r="I26" s="16" t="n"/>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
-      <c r="M26" s="16" t="n"/>
-      <c r="N26" s="16" t="n"/>
-      <c r="O26" s="16" t="n"/>
-      <c r="P26" s="16" t="n"/>
-      <c r="Q26" s="16" t="n"/>
-      <c r="R26" s="16" t="n"/>
-      <c r="S26" s="16" t="n"/>
-      <c r="T26" s="16" t="n"/>
+    <row r="25" ht="118" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>CR-023</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>Internationalisation</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Marchés cibles : 4 pays + structure géographique Pays → Ville → École</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>Restreindre aux 4 marchés de lancement (Bahreïn, Qatar, Tunisie, Libye) au lieu d’un support mondial générique. Cascade Pays → Ville → École : on choisit un pays, le système charge SES villes, on choisit une ville, on configure l’école. Aucune saisie libre de pays/ville. Données pays/villes en données de référence, extensibles.</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>Un acheteur du Golfe doit voir SON pays et SES villes, pas une liste mondiale ni la Tunisie par défaut. C’est ce qui rend la démo crédible pour Bahreïn/Qatar/Libye.</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>Paramètres · Onboarding · Console plateforme</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>#/app/settings · #/app/schools</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>owner, schooladmin</t>
+        </is>
+      </c>
+      <c r="M25" s="23" t="inlineStr">
+        <is>
+          <t>P1 - Immediate</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>TRIAGED</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <t>Sprint immédiat</t>
+        </is>
+      </c>
+      <c r="Q25" s="16" t="inlineStr">
+        <is>
+          <t>CR-004/005 (packs pays — FAIT), CR-017 (code école — FAIT)</t>
+        </is>
+      </c>
+      <c r="R25" s="16" t="inlineStr">
+        <is>
+          <t>Prolonge directement core/src/locales.js : remplacer les packs de démo FR/INTL par BH/QA/TN/LY + ajouter les villes. Faisable tout de suite, faible risque, fort impact démo. À FAIRE MAINTENANT.</t>
+        </is>
+      </c>
+      <c r="S25" s="16" t="inlineStr"/>
+      <c r="T25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26" ht="118" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>CR-024</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>ERP architecture</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Couche de configuration par pays (langue + système éducatif), un seul cœur</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>Un cœur ERP unique + des modules de configuration par pays (countries/{bahrain,qatar,tunisia,libye}). Chaque pays personnalise : langues (ordre primaire/secondaire), système éducatif (niveaux, matières, méthode d’évaluation, terminologie, structure de l’année). L’activation d’une école charge la bonne config. JAMAIS 4 bases de code.</t>
+        </is>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>Chaque école doit sentir qu’elle a un ERP local conçu pour SON système éducatif, pas un produit étranger traduit. C’est l’argument de vente régional.</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>Tout le produit</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t>owner, schooladmin</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>P2 - High</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>TRIAGED</t>
+        </is>
+      </c>
+      <c r="P26" s="16" t="inlineStr">
+        <is>
+          <t>À PHASER</t>
+        </is>
+      </c>
+      <c r="Q26" s="16" t="inlineStr">
+        <is>
+          <t>CR-023 (pays), CR-016/020 (modèle de rôles — FAIT)</t>
+        </is>
+      </c>
+      <c r="R26" s="16" t="inlineStr">
+        <is>
+          <t>À DÉCOUPER. La couche LANGUE existe déjà (i18n + packs pays) → activable vite. La couche CURRICULUM (niveaux/matières/évaluation/terminologie par pays) est le gros œuvre ERP : la faire pays par pays, à mesure que tu signes chaque marché. Ne PAS tout construire d’un coup.</t>
+        </is>
+      </c>
+      <c r="S26" s="16" t="inlineStr"/>
+      <c r="T26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n"/>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -34320,14 +34320,14 @@
           <t>M</t>
         </is>
       </c>
-      <c r="O25" s="16" t="inlineStr">
-        <is>
-          <t>TRIAGED</t>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="P25" s="16" t="inlineStr">
         <is>
-          <t>Sprint immédiat</t>
+          <t>5123df2 · 2026-07-23</t>
         </is>
       </c>
       <c r="Q25" s="16" t="inlineStr">
@@ -34341,7 +34341,11 @@
         </is>
       </c>
       <c r="S25" s="16" t="inlineStr"/>
-      <c r="T25" s="16" t="inlineStr"/>
+      <c r="T25" s="16" t="inlineStr">
+        <is>
+          <t>LIVRÉ. 4 pays (BH/QA/TN/LY) avec devise, code ISO, pièce d’identité et cadre légal locaux. Villes en données de référence, cascade Pays→Ville dans les Paramètres. La référence ERP porte le code pays (STD-LY-…). Ajouter un pays = un objet dans locales.js.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="118" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -34412,9 +34416,9 @@
           <t>XL</t>
         </is>
       </c>
-      <c r="O26" s="16" t="inlineStr">
-        <is>
-          <t>TRIAGED</t>
+      <c r="O26" s="22" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="P26" s="16" t="inlineStr">
@@ -34433,29 +34437,103 @@
         </is>
       </c>
       <c r="S26" s="16" t="inlineStr"/>
-      <c r="T26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
-      <c r="M27" s="16" t="n"/>
-      <c r="N27" s="16" t="n"/>
-      <c r="O27" s="16" t="n"/>
-      <c r="P27" s="16" t="n"/>
-      <c r="Q27" s="16" t="n"/>
-      <c r="R27" s="16" t="n"/>
-      <c r="S27" s="16" t="n"/>
-      <c r="T27" s="16" t="n"/>
+      <c r="T26" s="16" t="inlineStr">
+        <is>
+          <t>Couche LANGUE livrée avec CR-023 (languages par pays : primaire/secondaire). Reste la couche CURRICULUM (niveaux/matières/évaluation/terminologie par pays) = gros œuvre, à phaser marché par marché. Architecture prête : locales.js EST la couche de config par pays, un seul cœur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>CR-025</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>ERP architecture</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>La « Bible » d’architecture produit + références ERP à étudier</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>Constitution du produit : plateforme ERP régionale multi-pays / multi-tenant / multi-école / multi-langue (un seul cœur + config par pays). Deux identités (référence ERP vs identité humaine). API-first web+mobile. Sécurité (RBAC, isolation tenant, audit). Prêt IA. + références à étudier (ERPNext Education, Odoo, SAP/NetSuite/Dynamics) pour les PATTERNS, pas les interfaces.</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>Empêcher les sessions futures d’abîmer l’architecture peu à peu. Chaque changement se vérifie contre la Bible.</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>Tout le produit</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>docs/quality/ARCHITECTURE-BIBLE.md</t>
+        </is>
+      </c>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>P1 - Immediate</t>
+        </is>
+      </c>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O27" s="21" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P27" s="16" t="inlineStr">
+        <is>
+          <t>5123df2 · 2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q27" s="16" t="inlineStr">
+        <is>
+          <t>CR-004/005/016/017/018/020/023 (déjà faits)</t>
+        </is>
+      </c>
+      <c r="R27" s="16" t="inlineStr">
+        <is>
+          <t>LIVRÉ : docs/quality/ARCHITECTURE-BIBLE.md — la constitution, avec le tableau ÉTAT vs CIBLE (§11), la règle « classer avant de coder » (§12), le séquencement vers la vente (§13) et les références étudiées (§10). À ouvrir avant toute décision d’architecture.</t>
+        </is>
+      </c>
+      <c r="S27" s="16" t="inlineStr"/>
+      <c r="T27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="n"/>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -32343,10 +32343,14 @@
       </c>
       <c r="O3" s="16" t="inlineStr">
         <is>
-          <t>TRIAGED</t>
-        </is>
-      </c>
-      <c r="P3" s="16" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q3" s="16" t="inlineStr"/>
       <c r="R3" s="16" t="inlineStr">
         <is>
@@ -32356,7 +32360,7 @@
       <c r="S3" s="16" t="inlineStr"/>
       <c r="T3" s="16" t="inlineStr">
         <is>
-          <t>PAS un remplacer-tout. 1108 occurrences : 457 en commentaires (à laisser), 49 dans t() — où la chaîne FRANÇAISE est la CLÉ de traduction : la modifier casse l'arabe en silence, sans qu'aucun test n'échoue. Il faut modifier l'appel ET la clé i18n.js dans le même geste, et choisir au cas par cas (· ici, virgule là). ~600 décisions : mérite une passe dédiée.</t>
+          <t>LIVRÉ 2026-07-23. La passe de contenu (commit affa9ed) avait retiré 535 tirets du FR+AR ; il restait 3 tirets dans des chaînes RÉELLEMENT affichées : opsprofile.js (mode client) et 2 libellés d'autorité (locales.js BH/QA). Nettoyés (· et virgule). Recherche exhaustive : plus AUCUN tiret cadratin dans une chaîne rendue — il n'en reste que dans les commentaires de code (volontairement laissés). Critère d'acceptation atteint.</t>
         </is>
       </c>
     </row>
@@ -32794,10 +32798,14 @@
       </c>
       <c r="O8" s="22" t="inlineStr">
         <is>
-          <t>TRIAGED</t>
-        </is>
-      </c>
-      <c r="P8" s="16" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P8" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q8" s="16" t="inlineStr"/>
       <c r="R8" s="16" t="inlineStr">
         <is>
@@ -32811,7 +32819,7 @@
       </c>
       <c r="T8" s="16" t="inlineStr">
         <is>
-          <t>Le défaut « rien ne change au clic » est corrigé (DEF-003 : les ancres défilent + état actif). Des PAGES routées séparées avec URL propres restent un chantier plus large (SEO), à décider.</t>
+          <t>LIVRÉ 2026-07-23. La vitrine n'est plus une page unique à défilement : Accueil / Modules / Vos données / Tarifs / FAQ sont de VRAIES routes (#/, #/modules, #/donnees, #/tarifs, #/faq) sous une coquille partagée (app/src/pages/site/). URL propre partageable, bouton précédent respecté, entrée active marquée, accès direct à chaque page. Vérifié au navigateur (13/13) + e2e complet vert. Landing.jsx laissé en place, non importé.</t>
         </is>
       </c>
     </row>
@@ -33266,7 +33274,7 @@
       </c>
       <c r="T13" s="16" t="inlineStr">
         <is>
-          <t>Le débordement mobile réel est corrigé (DEF-001). La refonte visuelle complète de l’écran de connexion reste un choix de design d’Othman.</t>
+          <t>En attente du CHOIX d'Othman. 3 directions rendues et comparables (artefact « Coreon EDU · Connexion — 3 directions ») : 01 Cinématique (sombre, l'actuelle raffinée), 02 Clair éditorial (recommandée, alignée sur le site clair validé), 03 Focus (carte centrée minimale). La nouvelle accroche (CR-012) est déjà dans les trois. Dès qu'il choisit un numéro → câblage dans Login.jsx.</t>
         </is>
       </c>
     </row>
@@ -33340,10 +33348,14 @@
       </c>
       <c r="O14" s="22" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="P14" s="16" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q14" s="16" t="inlineStr"/>
       <c r="R14" s="16" t="inlineStr">
         <is>
@@ -33353,7 +33365,7 @@
       <c r="S14" s="16" t="inlineStr"/>
       <c r="T14" s="16" t="inlineStr">
         <is>
-          <t>Mention « Tunisie » retirée de l’écran de connexion. La réécriture des accroches marketing relève d’un choix éditorial.</t>
+          <t>LIVRÉ 2026-07-23. Accroche de connexion réécrite (les lignes qu'Othman jugeait peu attractives) : « Toute votre école, sur une seule plateforme. » + sous-titre admissions/évaluation/finances/communication. Ton international, plus « pas un ERP de plus ». FR + AR (i18n.js) dans le même geste. La refonte VISUELLE (couleurs/mise en page) relève de CR-011.</t>
         </is>
       </c>
     </row>
@@ -33804,7 +33816,7 @@
       <c r="S19" s="16" t="inlineStr"/>
       <c r="T19" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman. </t>
+          <t>SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman.   |  PLAN 2026-07-23 : docs/quality/erp-epics-plan.md — séquencement (CR-017 d'abord, faible risque ; CR-018 après un 2ᵉ marché) + 3 décisions à prendre (D-1 portée « vrai ERP », D-2 Person avant pilote ?, D-3 partie double ?). Rien n'est lancé : attend la décision d'Othman.</t>
         </is>
       </c>
     </row>
@@ -33891,7 +33903,7 @@
       <c r="S20" s="16" t="inlineStr"/>
       <c r="T20" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman. </t>
+          <t>SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman.   |  PLAN 2026-07-23 : docs/quality/erp-epics-plan.md — séquencement (CR-017 d'abord, faible risque ; CR-018 après un 2ᵉ marché) + 3 décisions à prendre (D-1 portée « vrai ERP », D-2 Person avant pilote ?, D-3 partie double ?). Rien n'est lancé : attend la décision d'Othman.</t>
         </is>
       </c>
     </row>
@@ -34160,7 +34172,7 @@
       <c r="S23" s="16" t="inlineStr"/>
       <c r="T23" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman. </t>
+          <t>SPÉCIFIÉ (plus bloqué par la recherche) : voir docs/quality/role-model.md §7 pour le backlog concret. Reste un chantier de plusieurs semaines qui touche le modèle de données — à planifier avec Othman.   |  PLAN 2026-07-23 : docs/quality/erp-epics-plan.md — séquencement (CR-017 d'abord, faible risque ; CR-018 après un 2ᵉ marché) + 3 décisions à prendre (D-1 portée « vrai ERP », D-2 Person avant pilote ?, D-3 partie double ?). Rien n'est lancé : attend la décision d'Othman.</t>
         </is>
       </c>
     </row>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -33257,10 +33257,14 @@
       </c>
       <c r="O13" s="22" t="inlineStr">
         <is>
-          <t>TRIAGED</t>
-        </is>
-      </c>
-      <c r="P13" s="16" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q13" s="16" t="inlineStr"/>
       <c r="R13" s="16" t="inlineStr">
         <is>
@@ -33274,7 +33278,7 @@
       </c>
       <c r="T13" s="16" t="inlineStr">
         <is>
-          <t>En attente du CHOIX d'Othman. 3 directions rendues et comparables (artefact « Coreon EDU · Connexion — 3 directions ») : 01 Cinématique (sombre, l'actuelle raffinée), 02 Clair éditorial (recommandée, alignée sur le site clair validé), 03 Focus (carte centrée minimale). La nouvelle accroche (CR-012) est déjà dans les trois. Dès qu'il choisit un numéro → câblage dans Login.jsx.</t>
+          <t>LIVRÉ 2026-07-23. Refonte de l'écran de connexion, direction « Clair éditorial » (choisie parmi 3 directions rendues) : fond clair aligné sur le site validé, formulaire à gauche, panneau marque à droite montrant la maquette produit en direct (évaluation). Violet Coreon en accent, logo en haut seulement, 0 débordement à 390px, mouvement coupé si réduit. Nouvelle accroche (CR-012) intégrée. Vérifié : 10/10 navigateur + suite e2e. DEF-001 déjà clos.</t>
         </is>
       </c>
     </row>

--- a/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
+++ b/docs/quality/Coreon-EDU_QA-Test-Workbook.xlsx
@@ -34648,70 +34648,254 @@
       <c r="T28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="16" t="n"/>
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>CR-027</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>ERP architecture / Role model</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>Imposer la séparation : retirer RH &amp; Comptabilité au compte Administration</t>
+        </is>
+      </c>
       <c r="H29" s="16" t="n"/>
-      <c r="I29" s="16" t="n"/>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
-      <c r="M29" s="16" t="n"/>
-      <c r="N29" s="16" t="n"/>
-      <c r="O29" s="16" t="n"/>
-      <c r="P29" s="16" t="n"/>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>La séparation des tâches est le fondement d'un vrai ERP et du contrôle interne ; sans elle CR-019 n'était que cosmétique.</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>Access control</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>/app/hr · /app/accounting · /app/finance · /app/budget · /app/staff · /app/recruit</t>
+        </is>
+      </c>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>admin, hr, accountant, schooladmin</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>P1 - Immediate</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="P29" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Q29" s="16" t="n"/>
       <c r="R29" s="16" t="n"/>
       <c r="S29" s="16" t="n"/>
-      <c r="T29" s="16" t="n"/>
+      <c r="T29" s="16" t="inlineStr">
+        <is>
+          <t>LIVRÉ 2026-07-23. Retiré de access.js ET nav.js (routes) ; acl.js : admin passe de '*' à « tout sauf RH &amp; argent » (HR_MONEY_COLLECTIONS) côté serveur. 3 tests d'exécution + 2 checks smoke-prod. Reste (chantier profondeur) : maker-checker + strip lecture admin — voir hr-accounting-module-spec.md §2/§5.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="16" t="n"/>
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>CR-028</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>ERP architecture / HR</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>Module RH : passer du squelette à un vrai module (recherche + profondeur)</t>
+        </is>
+      </c>
       <c r="H30" s="16" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
-      <c r="M30" s="16" t="n"/>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="16" t="n"/>
-      <c r="P30" s="16" t="n"/>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>La paie est le bloqueur Golfe (WPS, EOSB, salaire multi-composants) ; un ERP scolaire sans vraie RH ne se vend pas au-delà d'une crèche.</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>/app/hr · /app/staff · /app/recruit</t>
+        </is>
+      </c>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>hr, schooladmin</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>P2 - High</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="P30" s="16" t="inlineStr"/>
       <c r="Q30" s="16" t="n"/>
       <c r="R30" s="16" t="n"/>
       <c r="S30" s="16" t="n"/>
-      <c r="T30" s="16" t="n"/>
+      <c r="T30" s="16" t="inlineStr">
+        <is>
+          <t>SPÉCIFIÉ 2026-07-23 : docs/quality/hr-accounting-module-spec.md §3 (recherche NetSuite/ERPNext/Focus/GCC). Séquencement §5. À construire un sous-module à la fois. Gap actuel : salaire mono-montant, pas de bulletin, pas de WPS/EOSB, pas d'organigramme.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="16" t="n"/>
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>CR-029</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Othman</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>ERP architecture / Accounting</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>Module Comptabilité : socle comptable réel (recherche + profondeur)</t>
+        </is>
+      </c>
       <c r="H31" s="16" t="n"/>
-      <c r="I31" s="16" t="n"/>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
-      <c r="M31" s="16" t="n"/>
-      <c r="N31" s="16" t="n"/>
-      <c r="O31" s="16" t="n"/>
-      <c r="P31" s="16" t="n"/>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>Sans plan comptable, grand livre, balance/bilan et clôture, ce n'est pas de la comptabilité ; TVA + paiement en ligne = bloqueurs Golfe.</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>/app/accounting · /app/finance · /app/budget</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>accountant, schooladmin</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>P2 - High</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="P31" s="16" t="inlineStr"/>
       <c r="Q31" s="16" t="n"/>
       <c r="R31" s="16" t="n"/>
       <c r="S31" s="16" t="n"/>
-      <c r="T31" s="16" t="n"/>
+      <c r="T31" s="16" t="inlineStr">
+        <is>
+          <t>SPÉCIFIÉ 2026-07-23 : docs/quality/hr-accounting-module-spec.md §4 (recherche ERPNext/Tally/iSAMS/Edunext). La partie double = décision D-3 du plan des épics. Gap actuel : simple entrée, pas de plan comptable ni balance/bilan, pas d'AP, pas de rapprochement, pas de clôture.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="n"/>
